--- a/data/trans_dic/IP18_E_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP18_E_R-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92,8; 98,74</t>
+          <t>92,69; 98,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>89,02; 96,58</t>
+          <t>88,31; 96,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89,31; 96,66</t>
+          <t>88,87; 96,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78,04; 100,0</t>
+          <t>78,98; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,67; 97,08</t>
+          <t>89,55; 96,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,82; 99,57</t>
+          <t>95,98; 99,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,75; 97,97</t>
+          <t>92,36; 97,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>88,85; 100,0</t>
+          <t>88,7; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>92,34; 97,2</t>
+          <t>92,67; 97,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93,89; 97,82</t>
+          <t>93,64; 97,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91,78; 96,6</t>
+          <t>91,94; 96,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,68; 98,7</t>
+          <t>88,29; 98,71</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>90,83; 96,65</t>
+          <t>90,64; 96,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>95,85; 99,3</t>
+          <t>95,84; 99,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91,57; 96,45</t>
+          <t>91,58; 96,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78,24; 96,62</t>
+          <t>80,21; 96,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,85; 95,98</t>
+          <t>90,06; 95,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,44; 96,17</t>
+          <t>90,57; 96,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>93,23; 97,52</t>
+          <t>93,1; 97,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>88,12; 98,83</t>
+          <t>88,68; 98,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>91,53; 95,38</t>
+          <t>91,14; 95,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>93,94; 97,23</t>
+          <t>93,96; 97,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93,04; 96,51</t>
+          <t>93,04; 96,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>88,36; 97,03</t>
+          <t>88,32; 96,67</t>
         </is>
       </c>
     </row>
@@ -997,47 +997,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>86,71; 94,55</t>
+          <t>86,56; 94,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>89,11; 96,08</t>
+          <t>89,19; 96,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90,93; 97,1</t>
+          <t>91,4; 97,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43,2; 88,6</t>
+          <t>47,85; 87,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>87,74; 95,44</t>
+          <t>87,91; 95,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89,03; 95,49</t>
+          <t>88,73; 95,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>92,53; 97,79</t>
+          <t>92,16; 97,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>78,78; 100,0</t>
+          <t>76,44; 97,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>88,54; 94,12</t>
+          <t>88,4; 93,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>92,77; 96,7</t>
+          <t>92,62; 96,66</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>65,62; 91,47</t>
+          <t>66,95; 91,38</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,0; 95,84</t>
+          <t>89,18; 95,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>89,75; 96,03</t>
+          <t>90,46; 96,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90,1; 95,84</t>
+          <t>90,46; 96,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68,83; 92,96</t>
+          <t>67,75; 90,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,78; 95,45</t>
+          <t>88,76; 95,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,61; 96,2</t>
+          <t>90,6; 96,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,79; 93,1</t>
+          <t>86,13; 92,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>76,62; 97,1</t>
+          <t>78,51; 97,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>90,41; 94,68</t>
+          <t>90,18; 94,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91,56; 95,47</t>
+          <t>91,34; 95,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89,27; 94,01</t>
+          <t>89,49; 93,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76,97; 92,22</t>
+          <t>78,6; 92,52</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>91,89; 95,08</t>
+          <t>91,94; 94,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>93,15; 96,03</t>
+          <t>93,02; 96,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92,44; 95,38</t>
+          <t>92,38; 95,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74,35; 89,42</t>
+          <t>73,68; 89,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>91,27; 94,52</t>
+          <t>91,21; 94,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,05; 95,87</t>
+          <t>92,94; 95,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,6; 95,5</t>
+          <t>92,6; 95,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>89,6; 96,71</t>
+          <t>89,59; 96,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>92,03; 94,35</t>
+          <t>92,0; 94,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93,66; 95,71</t>
+          <t>93,75; 95,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92,98; 95,07</t>
+          <t>92,93; 95,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>84,51; 92,72</t>
+          <t>84,54; 92,72</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>106557; 113377</t>
+          <t>106433; 113395</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>116492; 126384</t>
+          <t>115573; 126143</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>109567; 118586</t>
+          <t>109029; 118264</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13309; 17054</t>
+          <t>13470; 17054</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>113866; 123270</t>
+          <t>113703; 123098</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>140151; 145630</t>
+          <t>140375; 145632</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>122090; 130364</t>
+          <t>122895; 130330</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19251; 21666</t>
+          <t>19219; 21666</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>223274; 235037</t>
+          <t>224070; 234635</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>260187; 271073</t>
+          <t>259495; 271134</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>234731; 247059</t>
+          <t>235129; 247145</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34337; 38217</t>
+          <t>34185; 38222</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>146140; 155505</t>
+          <t>145827; 155377</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>184654; 191306</t>
+          <t>184640; 191301</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>177523; 186991</t>
+          <t>177545; 187555</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22671; 27997</t>
+          <t>23241; 28014</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>159248; 170106</t>
+          <t>159625; 170010</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>187169; 199033</t>
+          <t>187430; 198934</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>194369; 203307</t>
+          <t>194084; 203751</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43825; 49155</t>
+          <t>44108; 49163</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>309495; 322519</t>
+          <t>308166; 322818</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>375401; 388515</t>
+          <t>375462; 389425</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>374329; 388293</t>
+          <t>374344; 388564</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>69550; 76375</t>
+          <t>69520; 76089</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>105529; 115068</t>
+          <t>105341; 114879</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>127076; 137011</t>
+          <t>127191; 136905</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>125135; 133620</t>
+          <t>125771; 133605</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11333; 23246</t>
+          <t>12554; 23006</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>115203; 125303</t>
+          <t>115423; 125240</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>139001; 149085</t>
+          <t>138534; 149472</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>135050; 142720</t>
+          <t>134498; 142767</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24958; 31680</t>
+          <t>24216; 30999</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>223997; 238120</t>
+          <t>223650; 237402</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>269765; 283893</t>
+          <t>269757; 283884</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>263063; 274209</t>
+          <t>262622; 274098</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38002; 52977</t>
+          <t>38776; 52923</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>172400; 183596</t>
+          <t>170825; 183161</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>179420; 191959</t>
+          <t>180824; 192521</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>173577; 184640</t>
+          <t>174276; 185073</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19306; 26073</t>
+          <t>19003; 25519</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>157876; 169725</t>
+          <t>157842; 169368</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>183445; 194752</t>
+          <t>183431; 194891</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>155779; 169043</t>
+          <t>156381; 168758</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21844; 27682</t>
+          <t>22384; 27868</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>333944; 349738</t>
+          <t>333096; 350533</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>368414; 384146</t>
+          <t>367497; 384280</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>334084; 351794</t>
+          <t>334900; 351546</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43535; 52157</t>
+          <t>44453; 52329</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>541227; 559988</t>
+          <t>541509; 559492</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>620381; 639591</t>
+          <t>619523; 640023</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>597946; 616934</t>
+          <t>597539; 616918</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74582; 89702</t>
+          <t>73912; 89845</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>559770; 579694</t>
+          <t>559408; 579792</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>662339; 682374</t>
+          <t>661538; 682051</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>619551; 638985</t>
+          <t>619529; 638715</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>117908; 127257</t>
+          <t>117893; 127020</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1106523; 1134395</t>
+          <t>1106063; 1134911</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1290435; 1318748</t>
+          <t>1291657; 1317988</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1223471; 1251004</t>
+          <t>1222887; 1251511</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>195974; 215015</t>
+          <t>196061; 215028</t>
         </is>
       </c>
     </row>
